--- a/templates/rota-data-file.xlsx
+++ b/templates/rota-data-file.xlsx
@@ -383,7 +383,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rota downloaded 2026-10-17T08:56 UTC. Keep this line and the column headings as they are; change the cells you need and upload the file under Set up → Data file → Update the rota.</t>
+          <t xml:space="preserve">Rota downloaded 2026-10-17T09:15 UTC. Keep this line and the column headings as they are; change the cells you need and upload the file under Set up → Data file → Update the rota.</t>
         </is>
       </c>
     </row>

--- a/templates/rota-data-file.xlsx
+++ b/templates/rota-data-file.xlsx
@@ -383,7 +383,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rota downloaded 2026-10-17T09:15 UTC. Keep this line and the column headings as they are; change the cells you need and upload the file under Set up → Data file → Update the rota.</t>
+          <t xml:space="preserve">Rota downloaded 2026-10-17T12:56 UTC. Keep this line and the column headings as they are; change the cells you need and upload the file under Set up → Data file → Update the rota.</t>
         </is>
       </c>
     </row>
